--- a/SFMC-Campaign-Brief-Template.xlsx
+++ b/SFMC-Campaign-Brief-Template.xlsx
@@ -791,7 +791,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>7281705</t>
+          <t>&lt;your EID&gt;</t>
         </is>
       </c>
     </row>
